--- a/TESSERA-GovernanceObject-ServiceSupportMap-ATFM.xlsx
+++ b/TESSERA-GovernanceObject-ServiceSupportMap-ATFM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P1350662\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P1350662\Downloads\TESSERA-Export\ATFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A29A61-C9D1-461C-889D-054C6277CBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F3EDF6-0902-455D-8BF0-77EF0BD3F1DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -181,9 +181,6 @@
     <t>Application Firewall Request</t>
   </si>
   <si>
-    <t>Service: Network::Firewall Policy::New/Modify</t>
-  </si>
-  <si>
     <t>ServiceProfile: Network Management</t>
   </si>
   <si>
@@ -205,9 +202,6 @@
     <t>StateBook: ICA::Platform::Application::Incident</t>
   </si>
   <si>
-    <t>Service: Infra Management::Connectivity Issue</t>
-  </si>
-  <si>
     <t>Application::Connectivity Issue</t>
   </si>
   <si>
@@ -293,6 +287,12 @@
   </si>
   <si>
     <t>Application System Unavailable Incident</t>
+  </si>
+  <si>
+    <t>Infra Management::Connectivity Issue</t>
+  </si>
+  <si>
+    <t>Network::Firewall Policy::New/Modify</t>
   </si>
 </sst>
 </file>
@@ -1154,13 +1154,13 @@
         <v>40</v>
       </c>
       <c r="L2" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="M2" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="N2" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
@@ -1168,28 +1168,28 @@
         <v>17</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="7" t="s">
+      <c r="L3" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N3" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
@@ -1197,25 +1197,25 @@
         <v>17</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>40</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>40</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
@@ -1223,28 +1223,28 @@
         <v>17</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
@@ -1252,25 +1252,25 @@
         <v>17</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>66</v>
-      </c>
       <c r="G6" s="6" t="s">
         <v>40</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
@@ -1278,28 +1278,28 @@
         <v>17</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="M7" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>67</v>
-      </c>
       <c r="N7" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
@@ -1307,25 +1307,25 @@
         <v>17</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>40</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
@@ -1333,28 +1333,28 @@
         <v>17</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>40</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
@@ -1362,25 +1362,25 @@
         <v>17</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="G10" s="6" t="s">
         <v>40</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
@@ -1388,28 +1388,28 @@
         <v>17</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>73</v>
-      </c>
       <c r="G11" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -1417,25 +1417,25 @@
         <v>17</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>40</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>40</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -1443,28 +1443,28 @@
         <v>17</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>40</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
@@ -1472,25 +1472,25 @@
         <v>17</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="G14" s="6" t="s">
         <v>40</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
@@ -1498,28 +1498,28 @@
         <v>17</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="G15" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
@@ -1527,25 +1527,25 @@
         <v>17</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>40</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>40</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
@@ -1553,28 +1553,28 @@
         <v>17</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>40</v>
       </c>
       <c r="F17" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="L17" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="G17" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="M17" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
